--- a/Resources/Economics.xlsx
+++ b/Resources/Economics.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KarienFerreira\Desktop\Project\COmbined\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KarienFerreira\Documents\GitHub\meadtagging\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C9A84B-C450-478D-8EC2-5C98CC0A467F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59A616A-197F-4341-9EC1-2D3DE308BFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-60" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Parameters" sheetId="1" r:id="rId1"/>
-    <sheet name="Loot Calc" sheetId="2" r:id="rId2"/>
+    <sheet name="Loot Calc" sheetId="2" r:id="rId1"/>
+    <sheet name="Parameters" sheetId="1" r:id="rId2"/>
     <sheet name="Adventure Levelling" sheetId="3" r:id="rId3"/>
     <sheet name="Evaluate Item" sheetId="6" r:id="rId4"/>
   </sheets>
@@ -287,7 +287,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -341,6 +341,18 @@
       <color theme="0"/>
       <name val="Verdana"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -555,7 +567,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -620,6 +632,26 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -834,54 +866,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11.1796875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="15.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2">
-        <v>2734</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -900,7 +884,7 @@
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="5">
-        <v>2734</v>
+        <v>3520</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -934,11 +918,14 @@
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="5">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="F2" s="4">
+        <f>25*3*2</f>
+        <v>150</v>
+      </c>
       <c r="G2" s="6"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -1074,15 +1061,15 @@
       <c r="B6" s="37"/>
       <c r="C6" s="10">
         <f>ROUNDUP(C1*1.5, 0)</f>
-        <v>4101</v>
+        <v>5280</v>
       </c>
       <c r="D6" s="11">
         <f>C6</f>
-        <v>4101</v>
+        <v>5280</v>
       </c>
       <c r="E6" s="12">
         <f>C6</f>
-        <v>4101</v>
+        <v>5280</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="6"/>
@@ -1115,15 +1102,15 @@
       <c r="B7" s="37"/>
       <c r="C7" s="10">
         <f>ROUNDDOWN(C2*C3/25, 0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" s="13">
         <f>AVERAGE(C7,E7)</f>
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E7" s="14">
         <f t="shared" ref="E7:E11" si="0">FLOOR(C7/2,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>14</v>
@@ -1158,15 +1145,15 @@
       <c r="B8" s="37"/>
       <c r="C8" s="10">
         <f>ROUNDUP(C2*C3/10, 0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D8" s="13">
         <f t="shared" ref="D8:D34" si="1">FLOOR(AVERAGE(C8,E8),1)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E8" s="14">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>16</v>
@@ -1201,15 +1188,15 @@
       <c r="B9" s="37"/>
       <c r="C9" s="10">
         <f>ROUNDUP(C1*C3/5, 0)</f>
-        <v>1641</v>
+        <v>2112</v>
       </c>
       <c r="D9" s="13">
         <f t="shared" si="1"/>
-        <v>1230</v>
+        <v>1584</v>
       </c>
       <c r="E9" s="14">
         <f t="shared" si="0"/>
-        <v>820</v>
+        <v>1056</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="6"/>
@@ -1242,15 +1229,15 @@
       <c r="B10" s="37"/>
       <c r="C10" s="10">
         <f>ROUND(C1*C3/5/10, 0)</f>
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="D10" s="13">
         <f t="shared" si="1"/>
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="E10" s="14">
         <f t="shared" si="0"/>
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>19</v>
@@ -1279,21 +1266,21 @@
       <c r="AB10" s="4"/>
     </row>
     <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="10">
+      <c r="B11" s="45"/>
+      <c r="C11" s="46">
         <f>ROUNDUP(C2*C3*2, 0)</f>
-        <v>96</v>
+        <v>150</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="47">
         <f t="shared" si="1"/>
-        <v>72</v>
+        <v>112</v>
       </c>
-      <c r="E11" s="14">
-        <f t="shared" si="0"/>
-        <v>48</v>
+      <c r="E11" s="48">
+        <f>FLOOR(C11/2,1)</f>
+        <v>75</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>21</v>
@@ -1327,15 +1314,15 @@
       </c>
       <c r="C12" s="16">
         <f>ROUND(C11*0.45, 0)</f>
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="D12" s="17">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E12" s="18">
         <f t="shared" ref="E12:E19" si="2">FLOOR(C12/3,1)</f>
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>23</v>
@@ -1370,15 +1357,15 @@
       </c>
       <c r="C13" s="16">
         <f>ROUND(C11*0.1, 0)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D13" s="17">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E13" s="18">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="6"/>
@@ -1411,15 +1398,15 @@
       </c>
       <c r="C14" s="16">
         <f>ROUND(C11*0.1, 0)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D14" s="17">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E14" s="18">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="6"/>
@@ -1452,15 +1439,15 @@
       </c>
       <c r="C15" s="16">
         <f>ROUND(C11*0.1, 0)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D15" s="17">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E15" s="18">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="6"/>
@@ -1493,15 +1480,15 @@
       </c>
       <c r="C16" s="16">
         <f>ROUND(C11*0.1, 0)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D16" s="17">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E16" s="18">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="6"/>
@@ -1534,15 +1521,15 @@
       </c>
       <c r="C17" s="16">
         <f>ROUND(C11*0.05, 0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" s="17">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="6"/>
@@ -1575,15 +1562,15 @@
       </c>
       <c r="C18" s="16">
         <f>ROUND(C11*0.05, 0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D18" s="17">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="6"/>
@@ -1616,15 +1603,15 @@
       </c>
       <c r="C19" s="16">
         <f>ROUND(C11*0.05, 0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" s="17">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E19" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="6"/>
@@ -1655,17 +1642,17 @@
         <v>31</v>
       </c>
       <c r="B20" s="37"/>
-      <c r="C20" s="10">
-        <f>ROUNDUP(C2*C3*2/10, 0)</f>
-        <v>10</v>
+      <c r="C20" s="46">
+        <f>ROUNDUP((C2*C3*2)/10, 0)</f>
+        <v>15</v>
       </c>
       <c r="D20" s="13">
         <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="E20" s="48">
+        <f>FLOOR(C20/2,1)</f>
         <v>7</v>
-      </c>
-      <c r="E20" s="14">
-        <f>FLOOR(C20/2,1)</f>
-        <v>5</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>32</v>
@@ -1700,15 +1687,15 @@
       </c>
       <c r="C21" s="16">
         <f>ROUND(C20*0.4, 0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D21" s="17">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" s="18">
         <f t="shared" ref="E21:E27" si="3">FLOOR(C21/3,1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="4"/>
@@ -1738,15 +1725,15 @@
       <c r="B22" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="49">
         <f>ROUND(C20*0.15, 0)</f>
         <v>2</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="50">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1779,15 +1766,15 @@
       <c r="B23" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="49">
         <f>ROUND(C20*0.15, 0)</f>
         <v>2</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="50">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1820,15 +1807,15 @@
       <c r="B24" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="49">
         <f>ROUND(C20*0.15, 0)</f>
         <v>2</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="50">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1984,15 +1971,15 @@
         <v>40</v>
       </c>
       <c r="B28" s="37"/>
-      <c r="C28" s="10">
+      <c r="C28" s="46">
         <f>ROUND(C2*C3/25, 0)</f>
+        <v>3</v>
+      </c>
+      <c r="D28" s="47">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D28" s="13">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
+      <c r="E28" s="48">
         <f>FLOOR(C28/2,1)</f>
         <v>1</v>
       </c>
@@ -2027,11 +2014,11 @@
       <c r="B29" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="49">
         <f>ROUND(C28*0.4, 0)</f>
         <v>1</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2067,7 +2054,7 @@
       <c r="B30" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="49">
         <f>ROUND(C28*0.15, 0)</f>
         <v>0</v>
       </c>
@@ -2108,7 +2095,7 @@
       <c r="B31" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="16">
+      <c r="C31" s="49">
         <f>ROUND(C28*0.15, 0)</f>
         <v>0</v>
       </c>
@@ -2149,7 +2136,7 @@
       <c r="B32" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="49">
         <f>ROUND(C28*0.15, 0)</f>
         <v>0</v>
       </c>
@@ -2190,7 +2177,7 @@
       <c r="B33" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="49">
         <f>ROUND(C28*0.05, 0)</f>
         <v>0</v>
       </c>
@@ -2231,12 +2218,12 @@
       <c r="B34" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="49">
         <f>ROUND(C28*0.05, 0)</f>
         <v>0</v>
       </c>
       <c r="D34" s="17">
-        <f t="shared" si="1"/>
+        <f>FLOOR(AVERAGE(C34,E34),1)</f>
         <v>0</v>
       </c>
       <c r="E34" s="18">
@@ -2272,7 +2259,7 @@
       <c r="B35" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="49">
         <f>ROUND(C28*0.05, 0)</f>
         <v>0</v>
       </c>
@@ -31140,6 +31127,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A1:B1"/>
@@ -31147,12 +31139,55 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A28:B28"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="11.1796875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>3520</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -31182,7 +31217,7 @@
       </c>
       <c r="B2" s="20">
         <f>Parameters!B1</f>
-        <v>2734</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31191,7 +31226,7 @@
       </c>
       <c r="B3" s="20">
         <f>Parameters!B2</f>
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31208,7 +31243,7 @@
       </c>
       <c r="B5" s="22">
         <f>B2/B3</f>
-        <v>170.875</v>
+        <v>140.80000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31217,7 +31252,7 @@
       </c>
       <c r="B6" s="20">
         <f>FLOOR(B5/10,1)-4</f>
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31226,7 +31261,7 @@
       </c>
       <c r="B7" s="20">
         <f>(FLOOR(B5/10,1)-4)*B4</f>
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31240,7 +31275,7 @@
       </c>
       <c r="B10" s="23">
         <f>B7*1</f>
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31249,7 +31284,7 @@
       </c>
       <c r="B11" s="24">
         <f>B7*1.2</f>
-        <v>62.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31258,7 +31293,7 @@
       </c>
       <c r="B12" s="25">
         <f>B7*1.5</f>
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31272,7 +31307,7 @@
       </c>
       <c r="B16" s="23">
         <f>B10*B1</f>
-        <v>1092</v>
+        <v>840</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31281,7 +31316,7 @@
       </c>
       <c r="B17" s="24">
         <f>B11*B1</f>
-        <v>1310.3999999999999</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31290,7 +31325,7 @@
       </c>
       <c r="B18" s="25">
         <f>B12*B1</f>
-        <v>1638</v>
+        <v>1260</v>
       </c>
     </row>
   </sheetData>
